--- a/research/traditional_assets/database/data/denmark/denmark_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07530000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="E2">
-        <v>0.135</v>
+        <v>0.021925</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001584445412382619</v>
+        <v>-0.0001529845316116576</v>
       </c>
       <c r="J2">
-        <v>-0.000129987720100836</v>
+        <v>-0.0001340901238783089</v>
       </c>
       <c r="K2">
-        <v>654.36</v>
+        <v>440.92</v>
       </c>
       <c r="L2">
-        <v>0.402831814823935</v>
+        <v>0.3424887369892807</v>
       </c>
       <c r="M2">
-        <v>260.49708</v>
+        <v>260.81626</v>
       </c>
       <c r="N2">
-        <v>0.03634927509942092</v>
+        <v>0.03889239051013257</v>
       </c>
       <c r="O2">
-        <v>0.3980944434256372</v>
+        <v>0.5915273972602739</v>
       </c>
       <c r="P2">
-        <v>79.79707999999999</v>
+        <v>126.71626</v>
       </c>
       <c r="Q2">
-        <v>0.01113473522640061</v>
+        <v>0.01889567110541149</v>
       </c>
       <c r="R2">
-        <v>0.1219467571367443</v>
+        <v>0.2873905923977139</v>
       </c>
       <c r="S2">
-        <v>180.7</v>
+        <v>134.1</v>
       </c>
       <c r="T2">
-        <v>0.6936738024088408</v>
+        <v>0.5141550607312596</v>
       </c>
       <c r="U2">
-        <v>3363.7</v>
+        <v>2587.5</v>
       </c>
       <c r="V2">
-        <v>0.4693644038233447</v>
+        <v>0.3858427401917657</v>
       </c>
       <c r="W2">
-        <v>0.1192758253461129</v>
+        <v>0.06571823617724902</v>
       </c>
       <c r="X2">
-        <v>0.04752938461951645</v>
+        <v>0.06527770073732098</v>
       </c>
       <c r="Y2">
-        <v>0.07174644072659643</v>
+        <v>0.0004405354399280442</v>
       </c>
       <c r="Z2">
-        <v>0.2732848166431786</v>
+        <v>0.2410522974316062</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04119057398842293</v>
+        <v>0.0586554771274831</v>
       </c>
       <c r="AC2">
-        <v>-0.04119057398842293</v>
+        <v>-0.0586554771274831</v>
       </c>
       <c r="AD2">
-        <v>3140.58</v>
+        <v>3128.83</v>
       </c>
       <c r="AE2">
-        <v>2.931886563937163</v>
+        <v>3.27976142998424</v>
       </c>
       <c r="AF2">
-        <v>3143.511886563937</v>
+        <v>3132.109761429984</v>
       </c>
       <c r="AG2">
-        <v>-220.1881134360628</v>
+        <v>544.6097614299842</v>
       </c>
       <c r="AH2">
-        <v>0.3048989585221117</v>
+        <v>0.3183617586310472</v>
       </c>
       <c r="AI2">
-        <v>0.3661627879029175</v>
+        <v>0.4245196011807564</v>
       </c>
       <c r="AJ2">
-        <v>-0.03169856422110368</v>
+        <v>0.07511123453417289</v>
       </c>
       <c r="AK2">
-        <v>-0.04217103253354305</v>
+        <v>0.1136851376057767</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>9545.835866261397</v>
+        <v>6816.623093681917</v>
       </c>
       <c r="AP2">
-        <v>-669.2647824804342</v>
+        <v>1186.513641459661</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06269999999999999</v>
+        <v>0.0373</v>
       </c>
       <c r="E3">
-        <v>0.09369999999999999</v>
+        <v>0.0489</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,91 +728,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.0004340258225757718</v>
+        <v>-0.000397321537213734</v>
       </c>
       <c r="J3">
-        <v>-0.0003489574702538565</v>
+        <v>-0.0003257543038025645</v>
       </c>
       <c r="K3">
-        <v>197</v>
+        <v>158.4</v>
       </c>
       <c r="L3">
-        <v>0.3322091062394604</v>
+        <v>0.3195481137784951</v>
       </c>
       <c r="M3">
-        <v>180.9</v>
+        <v>222.2</v>
       </c>
       <c r="N3">
-        <v>0.115598440794939</v>
+        <v>0.1203814064362336</v>
       </c>
       <c r="O3">
-        <v>0.918274111675127</v>
+        <v>1.402777777777778</v>
       </c>
       <c r="P3">
-        <v>41</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.0261997571729823</v>
+        <v>0.04772998157980279</v>
       </c>
       <c r="R3">
-        <v>0.2081218274111675</v>
+        <v>0.5561868686868686</v>
       </c>
       <c r="S3">
-        <v>139.9</v>
+        <v>134.1</v>
       </c>
       <c r="T3">
-        <v>0.7733554449972361</v>
+        <v>0.6035103510351035</v>
       </c>
       <c r="U3">
-        <v>716.9</v>
+        <v>865.5</v>
       </c>
       <c r="V3">
-        <v>0.45811233944661</v>
+        <v>0.4689023729548163</v>
       </c>
       <c r="W3">
-        <v>0.1227261400448542</v>
+        <v>0.0843360664465978</v>
       </c>
       <c r="X3">
-        <v>0.06204959055418957</v>
+        <v>0.07336325423199948</v>
       </c>
       <c r="Y3">
-        <v>0.06067654949066464</v>
+        <v>0.01097281221459832</v>
       </c>
       <c r="Z3">
-        <v>0.2697745315577776</v>
+        <v>0.1846265174035157</v>
       </c>
       <c r="AA3">
-        <v>-9.413983807132126e-05</v>
+        <v>-6.014288264027431e-05</v>
       </c>
       <c r="AB3">
-        <v>0.04042554288702958</v>
+        <v>0.05727653557039844</v>
       </c>
       <c r="AC3">
-        <v>-0.0405196827251009</v>
+        <v>-0.05733667845303871</v>
       </c>
       <c r="AD3">
-        <v>1520.3</v>
+        <v>1453.5</v>
       </c>
       <c r="AE3">
-        <v>2.931886563937163</v>
+        <v>3.27976142998424</v>
       </c>
       <c r="AF3">
-        <v>1523.231886563937</v>
+        <v>1456.779761429984</v>
       </c>
       <c r="AG3">
-        <v>806.3318865639372</v>
+        <v>591.2797614299843</v>
       </c>
       <c r="AH3">
-        <v>0.4932535081132131</v>
+        <v>0.4411035816434644</v>
       </c>
       <c r="AI3">
-        <v>0.447820781765728</v>
+        <v>0.4793647459976833</v>
       </c>
       <c r="AJ3">
-        <v>0.3400476735880785</v>
+        <v>0.2426181410997579</v>
       </c>
       <c r="AK3">
-        <v>0.3003621937216028</v>
+        <v>0.2720429110602655</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>4620.9726443769</v>
+        <v>3166.666666666667</v>
       </c>
       <c r="AP3">
-        <v>2450.856798066678</v>
+        <v>1288.191201372515</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nordfyns Bank A/S (CPSE:NRDF)</t>
+          <t>Totalbanken A/S (CPSE:TOTA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0799</v>
+        <v>0.114</v>
       </c>
       <c r="E4">
-        <v>0.144</v>
+        <v>0.0766</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>11</v>
+        <v>7.25</v>
       </c>
       <c r="L4">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>118.7</v>
+        <v>61.5</v>
       </c>
       <c r="V4">
-        <v>1.936378466557912</v>
+        <v>0.9290030211480362</v>
       </c>
       <c r="W4">
-        <v>0.1359703337453646</v>
+        <v>0.08734939759036145</v>
       </c>
       <c r="X4">
-        <v>0.05391059333910669</v>
+        <v>0.07098180199304957</v>
       </c>
       <c r="Y4">
-        <v>0.08205974040625794</v>
+        <v>0.01636759559731188</v>
       </c>
       <c r="Z4">
-        <v>0.400624349635796</v>
+        <v>0.2662993572084482</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04077129098780424</v>
+        <v>0.05759686689853102</v>
       </c>
       <c r="AC4">
-        <v>-0.04077129098780424</v>
+        <v>-0.05759686689853102</v>
       </c>
       <c r="AD4">
-        <v>35.7</v>
+        <v>42.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>35.7</v>
+        <v>42.8</v>
       </c>
       <c r="AG4">
-        <v>-83</v>
+        <v>-18.7</v>
       </c>
       <c r="AH4">
-        <v>0.3680412371134021</v>
+        <v>0.3926605504587156</v>
       </c>
       <c r="AI4">
-        <v>0.2824367088607595</v>
+        <v>0.3462783171521036</v>
       </c>
       <c r="AJ4">
-        <v>3.824884792626728</v>
+        <v>-0.3936842105263159</v>
       </c>
       <c r="AK4">
-        <v>-10.77922077922078</v>
+        <v>-0.3011272141706925</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Totalbanken A/S (CPSE:TOTA)</t>
+          <t>Vestjysk Bank A/S (CPSE:VJBA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.128</v>
+        <v>0.209</v>
       </c>
       <c r="E5">
-        <v>0.135</v>
+        <v>0.187</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>8.68</v>
+        <v>63.5</v>
       </c>
       <c r="L5">
-        <v>0.2874172185430464</v>
+        <v>0.2579203899268887</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>74.5</v>
+        <v>589.1</v>
       </c>
       <c r="V5">
-        <v>1.133942161339422</v>
+        <v>1.053657664103023</v>
       </c>
       <c r="W5">
-        <v>0.1133159268929504</v>
+        <v>0.07829839704069051</v>
       </c>
       <c r="X5">
-        <v>0.05262344285916351</v>
+        <v>0.06735336767258292</v>
       </c>
       <c r="Y5">
-        <v>0.06069248403378688</v>
+        <v>0.01094502936810759</v>
       </c>
       <c r="Z5">
-        <v>0.3871794871794872</v>
+        <v>0.3916640152720332</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04084225323446068</v>
+        <v>0.05820793299842442</v>
       </c>
       <c r="AC5">
-        <v>-0.04084225323446068</v>
+        <v>-0.05820793299842442</v>
       </c>
       <c r="AD5">
-        <v>34.2</v>
+        <v>239.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>34.2</v>
+        <v>239.9</v>
       </c>
       <c r="AG5">
-        <v>-40.3</v>
+        <v>-349.2</v>
       </c>
       <c r="AH5">
-        <v>0.3423423423423423</v>
+        <v>0.3002503128911139</v>
       </c>
       <c r="AI5">
-        <v>0.2905692438402719</v>
+        <v>0.2434544347473107</v>
       </c>
       <c r="AJ5">
-        <v>-1.586614173228346</v>
+        <v>-1.663649356836589</v>
       </c>
       <c r="AK5">
-        <v>-0.9328703703703702</v>
+        <v>-0.8811506434519306</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Skjern Bank A/S (CPSE:SKJE)</t>
+          <t>Ringkjøbing Landbobank A/S (CPSE:RILBA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.115</v>
+        <v>0.197</v>
       </c>
       <c r="E6">
-        <v>0.177</v>
+        <v>0.184</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>183.2</v>
       </c>
       <c r="L6">
-        <v>0.3639240506329114</v>
+        <v>0.5278017862287524</v>
       </c>
       <c r="M6">
-        <v>3.00768</v>
+        <v>24.8018</v>
       </c>
       <c r="N6">
-        <v>0.01980039499670836</v>
+        <v>0.006759457102365639</v>
       </c>
       <c r="O6">
-        <v>0.1307686956521739</v>
+        <v>0.1353810043668122</v>
       </c>
       <c r="P6">
-        <v>3.00768</v>
+        <v>24.8018</v>
       </c>
       <c r="Q6">
-        <v>0.01980039499670836</v>
+        <v>0.006759457102365639</v>
       </c>
       <c r="R6">
-        <v>0.1307686956521739</v>
+        <v>0.1353810043668122</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>357.6</v>
+        <v>585.6</v>
       </c>
       <c r="V6">
-        <v>2.354180381830151</v>
+        <v>0.1595988226316363</v>
       </c>
       <c r="W6">
-        <v>0.1353737492642731</v>
+        <v>0.1373004571685528</v>
       </c>
       <c r="X6">
-        <v>0.05128439811715797</v>
+        <v>0.06605046952689242</v>
       </c>
       <c r="Y6">
-        <v>0.08408935114711513</v>
+        <v>0.07124998764166038</v>
       </c>
       <c r="Z6">
-        <v>0.3226135783563042</v>
+        <v>0.2018492672714585</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04092247219556949</v>
+        <v>0.05847535159429378</v>
       </c>
       <c r="AC6">
-        <v>-0.04092247219556949</v>
+        <v>-0.05847535159429378</v>
       </c>
       <c r="AD6">
-        <v>69.3</v>
+        <v>1287.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>69.3</v>
+        <v>1287.9</v>
       </c>
       <c r="AG6">
-        <v>-288.3</v>
+        <v>702.3000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.3132911392405063</v>
+        <v>0.2598091626152387</v>
       </c>
       <c r="AI6">
-        <v>0.2703862660944206</v>
+        <v>0.5203636363636364</v>
       </c>
       <c r="AJ6">
-        <v>2.113636363636364</v>
+        <v>0.160654237675855</v>
       </c>
       <c r="AK6">
-        <v>2.846001974333662</v>
+        <v>0.3717053032708796</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vestjysk Bank A/S (CPSE:VJBA)</t>
+          <t>Nordfyns Bank A/S (CPSE:NRDF)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.208</v>
+        <v>0.025</v>
       </c>
       <c r="E7">
-        <v>0.868</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>146</v>
+        <v>4.25</v>
       </c>
       <c r="L7">
-        <v>0.6706476802939826</v>
+        <v>0.1534296028880867</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1249,55 +1249,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>461.7</v>
+        <v>105.9</v>
       </c>
       <c r="V7">
-        <v>0.7197194076383476</v>
+        <v>2.088757396449704</v>
       </c>
       <c r="W7">
-        <v>0.2895676318921063</v>
+        <v>0.04685777287761852</v>
       </c>
       <c r="X7">
-        <v>0.05085068255999421</v>
+        <v>0.06450493194774953</v>
       </c>
       <c r="Y7">
-        <v>0.2387169493321121</v>
+        <v>-0.01764715907013101</v>
       </c>
       <c r="Z7">
-        <v>0.4262776581163109</v>
+        <v>3.597402597402596</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04094999663063299</v>
+        <v>0.05883560266067243</v>
       </c>
       <c r="AC7">
-        <v>-0.04094999663063299</v>
+        <v>-0.05883560266067243</v>
       </c>
       <c r="AD7">
-        <v>279.3</v>
+        <v>13.1</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>279.3</v>
+        <v>13.1</v>
       </c>
       <c r="AG7">
-        <v>-182.4</v>
+        <v>-92.80000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.3033231972198089</v>
+        <v>0.2053291536050157</v>
       </c>
       <c r="AI7">
-        <v>0.2561680271484912</v>
+        <v>0.1396588486140725</v>
       </c>
       <c r="AJ7">
-        <v>-0.3972990633848834</v>
+        <v>2.204275534441805</v>
       </c>
       <c r="AK7">
-        <v>-0.2901686286986955</v>
+        <v>7.669421487603302</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Møns Bank A/S (CPSE:MNBA)</t>
+          <t>Danske Andelskassers Bank A/S (CPSE:DAB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0703</v>
+        <v>0.0076</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>-0.00505</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1341,82 +1341,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>6.79</v>
+        <v>15.8</v>
       </c>
       <c r="L8">
-        <v>0.2433691756272402</v>
+        <v>0.1899038461538461</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.03594034194252456</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.6253164556962025</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.03594034194252456</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.6253164556962025</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>272.7</v>
+        <v>166.6</v>
       </c>
       <c r="V8">
-        <v>4.391304347826087</v>
+        <v>0.6060385594761731</v>
       </c>
       <c r="W8">
-        <v>0.0889908256880734</v>
+        <v>0.04574406485234511</v>
       </c>
       <c r="X8">
-        <v>0.04943026047661911</v>
+        <v>0.06429676329148318</v>
       </c>
       <c r="Y8">
-        <v>0.03956056521145429</v>
+        <v>-0.01855269843913807</v>
       </c>
       <c r="Z8">
-        <v>0.3236658932714617</v>
+        <v>0.88135593220339</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04104601229424932</v>
+        <v>0.05888821789439044</v>
       </c>
       <c r="AC8">
-        <v>-0.04104601229424932</v>
+        <v>-0.05888821789439044</v>
       </c>
       <c r="AD8">
-        <v>22.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>22.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AG8">
-        <v>-249.9</v>
+        <v>-99</v>
       </c>
       <c r="AH8">
-        <v>0.2685512367491166</v>
+        <v>0.1973722627737226</v>
       </c>
       <c r="AI8">
-        <v>0.2175572519083969</v>
+        <v>0.1804109954630371</v>
       </c>
       <c r="AJ8">
-        <v>1.330670926517572</v>
+        <v>-0.5628197839681638</v>
       </c>
       <c r="AK8">
-        <v>1.488385944014294</v>
+        <v>-0.4757328207592503</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1436,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ringkjøbing Landbobank A/S (CPSE:RILBA)</t>
+          <t>Fynske Bank A/S (CPSE:FYNBK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1442,10 +1445,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.191</v>
+        <v>-0.0257</v>
       </c>
       <c r="E9">
-        <v>0.171</v>
+        <v>-0.271</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,28 +1463,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>177.2</v>
+        <v>2.17</v>
       </c>
       <c r="L9">
-        <v>0.5028376844494892</v>
+        <v>0.06235632183908046</v>
       </c>
       <c r="M9">
-        <v>30.956</v>
+        <v>2.82734</v>
       </c>
       <c r="N9">
-        <v>0.008141388107198274</v>
+        <v>0.01996709039548023</v>
       </c>
       <c r="O9">
-        <v>0.1746952595936795</v>
+        <v>1.302921658986175</v>
       </c>
       <c r="P9">
-        <v>30.956</v>
+        <v>2.82734</v>
       </c>
       <c r="Q9">
-        <v>0.008141388107198274</v>
+        <v>0.01996709039548023</v>
       </c>
       <c r="R9">
-        <v>0.1746952595936795</v>
+        <v>1.302921658986175</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1490,55 +1493,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>519.6</v>
+        <v>105.7</v>
       </c>
       <c r="V9">
-        <v>0.1366541303947611</v>
+        <v>0.7464689265536724</v>
       </c>
       <c r="W9">
-        <v>0.14247808957144</v>
+        <v>0.01172339276066991</v>
       </c>
       <c r="X9">
-        <v>0.04752938461951645</v>
+        <v>0.06257381260553026</v>
       </c>
       <c r="Y9">
-        <v>0.09494870495192359</v>
+        <v>-0.05085041984486035</v>
       </c>
       <c r="Z9">
-        <v>0.1793658064844506</v>
+        <v>0.455497382198953</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04119057398842293</v>
+        <v>0.05936780386244181</v>
       </c>
       <c r="AC9">
-        <v>-0.04119057398842293</v>
+        <v>-0.05936780386244181</v>
       </c>
       <c r="AD9">
-        <v>1048.8</v>
+        <v>20.2</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1048.8</v>
+        <v>20.2</v>
       </c>
       <c r="AG9">
-        <v>529.1999999999999</v>
+        <v>-85.5</v>
       </c>
       <c r="AH9">
-        <v>0.2161983879944755</v>
+        <v>0.1248454882571075</v>
       </c>
       <c r="AI9">
-        <v>0.4400990306743318</v>
+        <v>0.1145124716553288</v>
       </c>
       <c r="AJ9">
-        <v>0.1221747662472584</v>
+        <v>-1.524064171122995</v>
       </c>
       <c r="AK9">
-        <v>0.2839817547625436</v>
+        <v>-1.209335219236209</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1555,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hvidbjerg Bank A/S (CPSE:HVID)</t>
+          <t>Kreditbanken A/S (CPSE:KRE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,10 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0726</v>
+        <v>0.0299</v>
       </c>
       <c r="E10">
-        <v>0.061</v>
+        <v>-0.0115</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,691 +1585,90 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3.18</v>
+        <v>6.35</v>
       </c>
       <c r="L10">
-        <v>0.2321167883211679</v>
+        <v>0.2679324894514768</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>1.10712</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.01122839756592292</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.1743496062992126</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>1.10712</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.01122839756592292</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.1743496062992126</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>54.9</v>
+        <v>107.6</v>
       </c>
       <c r="V10">
-        <v>2.003649635036497</v>
+        <v>1.091277890466531</v>
       </c>
       <c r="W10">
-        <v>0.1177777777777778</v>
+        <v>0.05313807531380753</v>
       </c>
       <c r="X10">
-        <v>0.04696124742661904</v>
+        <v>0.06084152867983689</v>
       </c>
       <c r="Y10">
-        <v>0.07081653035115874</v>
+        <v>-0.007703453366029359</v>
       </c>
       <c r="Z10">
-        <v>0.5490981963927856</v>
+        <v>1.169215589541194</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04123788544014598</v>
+        <v>0.05994609731359873</v>
       </c>
       <c r="AC10">
-        <v>-0.04123788544014598</v>
+        <v>-0.05994609731359873</v>
       </c>
       <c r="AD10">
-        <v>6.81</v>
+        <v>3.83</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>6.81</v>
+        <v>3.83</v>
       </c>
       <c r="AG10">
-        <v>-48.09</v>
+        <v>-103.77</v>
       </c>
       <c r="AH10">
-        <v>0.1990646009938614</v>
+        <v>0.03739138924143318</v>
       </c>
       <c r="AI10">
-        <v>0.1865242399342646</v>
+        <v>0.03477708163079997</v>
       </c>
       <c r="AJ10">
-        <v>2.324311261478976</v>
+        <v>20.07156673114119</v>
       </c>
       <c r="AK10">
-        <v>2.615008156606852</v>
+        <v>-41.01581027667982</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Fynske Bank A/S (CPSE:FYNBK)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.0208</v>
-      </c>
-      <c r="E11">
-        <v>0.026</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>9.51</v>
-      </c>
-      <c r="L11">
-        <v>0.2014830508474576</v>
-      </c>
-      <c r="M11">
-        <v>1.86468</v>
-      </c>
-      <c r="N11">
-        <v>0.01252303559435863</v>
-      </c>
-      <c r="O11">
-        <v>0.1960757097791798</v>
-      </c>
-      <c r="P11">
-        <v>1.86468</v>
-      </c>
-      <c r="Q11">
-        <v>0.01252303559435863</v>
-      </c>
-      <c r="R11">
-        <v>0.1960757097791798</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>138.9</v>
-      </c>
-      <c r="V11">
-        <v>0.9328408327736736</v>
-      </c>
-      <c r="W11">
-        <v>0.05309882747068677</v>
-      </c>
-      <c r="X11">
-        <v>0.0460095374985247</v>
-      </c>
-      <c r="Y11">
-        <v>0.007089289972162065</v>
-      </c>
-      <c r="Z11">
-        <v>0.3647604327666152</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.04132194954882596</v>
-      </c>
-      <c r="AC11">
-        <v>-0.04132194954882596</v>
-      </c>
-      <c r="AD11">
-        <v>30.2</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>30.2</v>
-      </c>
-      <c r="AG11">
-        <v>-108.7</v>
-      </c>
-      <c r="AH11">
-        <v>0.1686208821887214</v>
-      </c>
-      <c r="AI11">
-        <v>0.1402693915466791</v>
-      </c>
-      <c r="AJ11">
-        <v>-2.703980099502488</v>
-      </c>
-      <c r="AK11">
-        <v>-1.422774869109948</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Danske Andelskassers Bank A/S (CPSE:DAB)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0.731</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>30</v>
-      </c>
-      <c r="L12">
-        <v>0.2822201317027281</v>
-      </c>
-      <c r="M12">
-        <v>42.45999999999999</v>
-      </c>
-      <c r="N12">
-        <v>0.1412978369384359</v>
-      </c>
-      <c r="O12">
-        <v>1.415333333333333</v>
-      </c>
-      <c r="P12">
-        <v>1.66</v>
-      </c>
-      <c r="Q12">
-        <v>0.005524126455906822</v>
-      </c>
-      <c r="R12">
-        <v>0.05533333333333333</v>
-      </c>
-      <c r="S12">
-        <v>40.8</v>
-      </c>
-      <c r="T12">
-        <v>0.9609043805934998</v>
-      </c>
-      <c r="U12">
-        <v>193.9</v>
-      </c>
-      <c r="V12">
-        <v>0.6452579034941764</v>
-      </c>
-      <c r="W12">
-        <v>0.09496676163342831</v>
-      </c>
-      <c r="X12">
-        <v>0.04590925795426323</v>
-      </c>
-      <c r="Y12">
-        <v>0.04905750367916508</v>
-      </c>
-      <c r="Z12">
-        <v>0.4337005303957569</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.0413311808485344</v>
-      </c>
-      <c r="AC12">
-        <v>-0.0413311808485344</v>
-      </c>
-      <c r="AD12">
-        <v>59.5</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>59.5</v>
-      </c>
-      <c r="AG12">
-        <v>-134.4</v>
-      </c>
-      <c r="AH12">
-        <v>0.1652777777777778</v>
-      </c>
-      <c r="AI12">
-        <v>0.1484160638563233</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.8091511137868754</v>
-      </c>
-      <c r="AK12">
-        <v>-0.6492753623188406</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Djurslands Bank A/S (CPSE:DJUR)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.07530000000000001</v>
-      </c>
-      <c r="E13">
-        <v>0.122</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>15.1</v>
-      </c>
-      <c r="L13">
-        <v>0.2431561996779388</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>-0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>-0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>238.1</v>
-      </c>
-      <c r="V13">
-        <v>1.731636363636364</v>
-      </c>
-      <c r="W13">
-        <v>0.08301264431006047</v>
-      </c>
-      <c r="X13">
-        <v>0.04472455208141633</v>
-      </c>
-      <c r="Y13">
-        <v>0.03828809222864415</v>
-      </c>
-      <c r="Z13">
-        <v>0.2856485740570378</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.04144613950611194</v>
-      </c>
-      <c r="AC13">
-        <v>-0.04144613950611194</v>
-      </c>
-      <c r="AD13">
-        <v>19.4</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>19.4</v>
-      </c>
-      <c r="AG13">
-        <v>-218.7</v>
-      </c>
-      <c r="AH13">
-        <v>0.1236456341618865</v>
-      </c>
-      <c r="AI13">
-        <v>0.09040074557315936</v>
-      </c>
-      <c r="AJ13">
-        <v>2.693349753694581</v>
-      </c>
-      <c r="AK13">
-        <v>9.306382978723404</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Lollands Bank A/S (CPSE:LOLB)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.0482</v>
-      </c>
-      <c r="E14">
-        <v>0.0303</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>11.2</v>
-      </c>
-      <c r="L14">
-        <v>0.3236994219653179</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>-0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>-0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>112.8</v>
-      </c>
-      <c r="V14">
-        <v>1.194915254237288</v>
-      </c>
-      <c r="W14">
-        <v>0.1192758253461129</v>
-      </c>
-      <c r="X14">
-        <v>0.0440147291461678</v>
-      </c>
-      <c r="Y14">
-        <v>0.07526109619994509</v>
-      </c>
-      <c r="Z14">
-        <v>0.3368708012851719</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.04152068045183221</v>
-      </c>
-      <c r="AC14">
-        <v>-0.04152068045183221</v>
-      </c>
-      <c r="AD14">
-        <v>10.1</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>10.1</v>
-      </c>
-      <c r="AG14">
-        <v>-102.7</v>
-      </c>
-      <c r="AH14">
-        <v>0.09665071770334928</v>
-      </c>
-      <c r="AI14">
-        <v>0.08859649122807017</v>
-      </c>
-      <c r="AJ14">
-        <v>12.37349397590362</v>
-      </c>
-      <c r="AK14">
-        <v>-85.58333333333313</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kreditbanken A/S (CPSE:KRE)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.141</v>
-      </c>
-      <c r="E15">
-        <v>0.272</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>15.7</v>
-      </c>
-      <c r="L15">
-        <v>0.4175531914893617</v>
-      </c>
-      <c r="M15">
-        <v>1.30872</v>
-      </c>
-      <c r="N15">
-        <v>0.01210656799259945</v>
-      </c>
-      <c r="O15">
-        <v>0.0833579617834395</v>
-      </c>
-      <c r="P15">
-        <v>1.30872</v>
-      </c>
-      <c r="Q15">
-        <v>0.01210656799259945</v>
-      </c>
-      <c r="R15">
-        <v>0.0833579617834395</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>103.4</v>
-      </c>
-      <c r="V15">
-        <v>0.9565217391304349</v>
-      </c>
-      <c r="W15">
-        <v>0.1475563909774436</v>
-      </c>
-      <c r="X15">
-        <v>0.04259055854239098</v>
-      </c>
-      <c r="Y15">
-        <v>0.1049658324350526</v>
-      </c>
-      <c r="Z15">
-        <v>0.3970852254725948</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.04168499995178693</v>
-      </c>
-      <c r="AC15">
-        <v>-0.04168499995178693</v>
-      </c>
-      <c r="AD15">
-        <v>4.17</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>4.17</v>
-      </c>
-      <c r="AG15">
-        <v>-99.23</v>
-      </c>
-      <c r="AH15">
-        <v>0.03714260265431549</v>
-      </c>
-      <c r="AI15">
-        <v>0.03371876768820247</v>
-      </c>
-      <c r="AJ15">
-        <v>-11.1871476888388</v>
-      </c>
-      <c r="AK15">
-        <v>-4.895411938825852</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/denmark/denmark_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0336</v>
+        <v>0.116</v>
       </c>
       <c r="E2">
-        <v>0.021925</v>
+        <v>0.19</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,103 +600,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001529845316116576</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>-0.0001340901238783089</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>440.92</v>
+        <v>867.5</v>
       </c>
       <c r="L2">
-        <v>0.3424887369892807</v>
+        <v>0.4561707945522427</v>
       </c>
       <c r="M2">
-        <v>260.81626</v>
+        <v>270.81454</v>
       </c>
       <c r="N2">
-        <v>0.03889239051013257</v>
+        <v>0.03746172275940297</v>
       </c>
       <c r="O2">
-        <v>0.5915273972602739</v>
+        <v>0.3121781440922191</v>
       </c>
       <c r="P2">
-        <v>126.71626</v>
+        <v>143.41454</v>
       </c>
       <c r="Q2">
-        <v>0.01889567110541149</v>
+        <v>0.0198385054847768</v>
       </c>
       <c r="R2">
-        <v>0.2873905923977139</v>
+        <v>0.1653193544668588</v>
       </c>
       <c r="S2">
-        <v>134.1</v>
+        <v>127.4</v>
       </c>
       <c r="T2">
-        <v>0.5141550607312596</v>
+        <v>0.4704326436830164</v>
       </c>
       <c r="U2">
-        <v>2587.5</v>
+        <v>2044.9</v>
       </c>
       <c r="V2">
-        <v>0.3858427401917657</v>
+        <v>0.2828706201325199</v>
       </c>
       <c r="W2">
-        <v>0.06571823617724902</v>
+        <v>0.1777330650570087</v>
       </c>
       <c r="X2">
-        <v>0.06527770073732098</v>
+        <v>0.0541345875174358</v>
       </c>
       <c r="Y2">
-        <v>0.0004405354399280442</v>
+        <v>0.1235984775395729</v>
       </c>
       <c r="Z2">
-        <v>0.2410522974316062</v>
+        <v>0.4113624908878136</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0586554771274831</v>
+        <v>0.05126086038812895</v>
       </c>
       <c r="AC2">
-        <v>-0.0586554771274831</v>
+        <v>-0.05126086038812895</v>
       </c>
       <c r="AD2">
-        <v>3128.83</v>
+        <v>3526.5</v>
       </c>
       <c r="AE2">
-        <v>3.27976142998424</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>3132.109761429984</v>
+        <v>3526.5</v>
       </c>
       <c r="AG2">
-        <v>544.6097614299842</v>
+        <v>1481.6</v>
       </c>
       <c r="AH2">
-        <v>0.3183617586310472</v>
+        <v>0.3278757112573915</v>
       </c>
       <c r="AI2">
-        <v>0.4245196011807564</v>
+        <v>0.4041277990419656</v>
       </c>
       <c r="AJ2">
-        <v>0.07511123453417289</v>
+        <v>0.1700896598436406</v>
       </c>
       <c r="AK2">
-        <v>0.1136851376057767</v>
+        <v>0.2217532516127101</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>6816.623093681917</v>
-      </c>
-      <c r="AP2">
-        <v>1186.513641459661</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0373</v>
+        <v>0.116</v>
       </c>
       <c r="E3">
-        <v>0.0489</v>
+        <v>0.184</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,103 +722,97 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.000397321537213734</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.0003257543038025645</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>158.4</v>
+        <v>343.2</v>
       </c>
       <c r="L3">
-        <v>0.3195481137784951</v>
+        <v>0.4341555977229601</v>
       </c>
       <c r="M3">
-        <v>222.2</v>
+        <v>210.5</v>
       </c>
       <c r="N3">
-        <v>0.1203814064362336</v>
+        <v>0.1131416285944638</v>
       </c>
       <c r="O3">
-        <v>1.402777777777778</v>
+        <v>0.6133449883449884</v>
       </c>
       <c r="P3">
-        <v>88.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.04772998157980279</v>
+        <v>0.04466541252351518</v>
       </c>
       <c r="R3">
-        <v>0.5561868686868686</v>
+        <v>0.2421328671328671</v>
       </c>
       <c r="S3">
-        <v>134.1</v>
+        <v>127.4</v>
       </c>
       <c r="T3">
-        <v>0.6035103510351035</v>
+        <v>0.6052256532066509</v>
       </c>
       <c r="U3">
-        <v>865.5</v>
+        <v>263.2</v>
       </c>
       <c r="V3">
-        <v>0.4689023729548163</v>
+        <v>0.1414673474872346</v>
       </c>
       <c r="W3">
-        <v>0.0843360664465978</v>
+        <v>0.2169131588926811</v>
       </c>
       <c r="X3">
-        <v>0.07336325423199948</v>
+        <v>0.06195421273469429</v>
       </c>
       <c r="Y3">
-        <v>0.01097281221459832</v>
+        <v>0.1549589461579868</v>
       </c>
       <c r="Z3">
-        <v>0.1846265174035157</v>
+        <v>0.3642521426596627</v>
       </c>
       <c r="AA3">
-        <v>-6.014288264027431e-05</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05727653557039844</v>
+        <v>0.04908217912978664</v>
       </c>
       <c r="AC3">
-        <v>-0.05733667845303871</v>
+        <v>-0.04908217912978664</v>
       </c>
       <c r="AD3">
-        <v>1453.5</v>
+        <v>1716.9</v>
       </c>
       <c r="AE3">
-        <v>3.27976142998424</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1456.779761429984</v>
+        <v>1716.9</v>
       </c>
       <c r="AG3">
-        <v>591.2797614299843</v>
+        <v>1453.7</v>
       </c>
       <c r="AH3">
-        <v>0.4411035816434644</v>
+        <v>0.4799295577793929</v>
       </c>
       <c r="AI3">
-        <v>0.4793647459976833</v>
+        <v>0.4731968139349007</v>
       </c>
       <c r="AJ3">
-        <v>0.2426181410997579</v>
+        <v>0.4386277231307706</v>
       </c>
       <c r="AK3">
-        <v>0.2720429110602655</v>
+        <v>0.4319931057026537</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>3166.666666666667</v>
-      </c>
-      <c r="AP3">
-        <v>1288.191201372515</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Totalbanken A/S (CPSE:TOTA)</t>
+          <t>Vestjysk Bank A/S (CPSE:VJBA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.114</v>
+        <v>0.254</v>
       </c>
       <c r="E4">
-        <v>0.0766</v>
+        <v>0.392</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,82 +850,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7.25</v>
+        <v>132.5</v>
       </c>
       <c r="L4">
-        <v>0.25</v>
+        <v>0.4348539547095504</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>19.7344</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02773633169360506</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1489388679245283</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>19.7344</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02773633169360506</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1489388679245283</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>61.5</v>
+        <v>473.9</v>
       </c>
       <c r="V4">
-        <v>0.9290030211480362</v>
+        <v>0.6660576247364722</v>
       </c>
       <c r="W4">
-        <v>0.08734939759036145</v>
+        <v>0.1777330650570087</v>
       </c>
       <c r="X4">
-        <v>0.07098180199304957</v>
+        <v>0.05742179819299602</v>
       </c>
       <c r="Y4">
-        <v>0.01636759559731188</v>
+        <v>0.1203112668640127</v>
       </c>
       <c r="Z4">
-        <v>0.2662993572084482</v>
+        <v>0.7688619732525865</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05759686689853102</v>
+        <v>0.0500799072990732</v>
       </c>
       <c r="AC4">
-        <v>-0.05759686689853102</v>
+        <v>-0.0500799072990732</v>
       </c>
       <c r="AD4">
-        <v>42.8</v>
+        <v>349.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>42.8</v>
+        <v>349.5</v>
       </c>
       <c r="AG4">
-        <v>-18.7</v>
+        <v>-124.4</v>
       </c>
       <c r="AH4">
-        <v>0.3926605504587156</v>
+        <v>0.3294062205466541</v>
       </c>
       <c r="AI4">
-        <v>0.3462783171521036</v>
+        <v>0.2715617715617716</v>
       </c>
       <c r="AJ4">
-        <v>-0.3936842105263159</v>
+        <v>-0.2118889456651337</v>
       </c>
       <c r="AK4">
-        <v>-0.3011272141706925</v>
+        <v>-0.1529947115975894</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vestjysk Bank A/S (CPSE:VJBA)</t>
+          <t>Ringkjøbing Landbobank A/S (CPSE:RILBA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.209</v>
+        <v>0.215</v>
       </c>
       <c r="E5">
-        <v>0.187</v>
+        <v>0.258</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,82 +972,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>63.5</v>
+        <v>283.6</v>
       </c>
       <c r="L5">
-        <v>0.2579203899268887</v>
+        <v>0.562029330162505</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>26.0166</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.006755979121763744</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.09173695345557122</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>26.0166</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.006755979121763744</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.09173695345557122</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>589.1</v>
+        <v>740.9</v>
       </c>
       <c r="V5">
-        <v>1.053657664103023</v>
+        <v>0.1923965826170506</v>
       </c>
       <c r="W5">
-        <v>0.07829839704069051</v>
+        <v>0.2389015247241176</v>
       </c>
       <c r="X5">
-        <v>0.06735336767258292</v>
+        <v>0.05593579365513608</v>
       </c>
       <c r="Y5">
-        <v>0.01094502936810759</v>
+        <v>0.1829657310689816</v>
       </c>
       <c r="Z5">
-        <v>0.3916640152720332</v>
+        <v>0.2854395293585247</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05820793299842442</v>
+        <v>0.05054592236889402</v>
       </c>
       <c r="AC5">
-        <v>-0.05820793299842442</v>
+        <v>-0.05054592236889402</v>
       </c>
       <c r="AD5">
-        <v>239.9</v>
+        <v>1346.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>239.9</v>
+        <v>1346.7</v>
       </c>
       <c r="AG5">
-        <v>-349.2</v>
+        <v>605.8000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.3002503128911139</v>
+        <v>0.2591003540095428</v>
       </c>
       <c r="AI5">
-        <v>0.2434544347473107</v>
+        <v>0.4859978347167088</v>
       </c>
       <c r="AJ5">
-        <v>-1.663649356836589</v>
+        <v>0.1359301725491956</v>
       </c>
       <c r="AK5">
-        <v>-0.8811506434519306</v>
+        <v>0.2984089453721492</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ringkjøbing Landbobank A/S (CPSE:RILBA)</t>
+          <t>Djurslands Bank A/S (CPSE:DJUR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.197</v>
+        <v>0.117</v>
       </c>
       <c r="E6">
-        <v>0.184</v>
+        <v>0.21</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>183.2</v>
+        <v>32.3</v>
       </c>
       <c r="L6">
-        <v>0.5278017862287524</v>
+        <v>0.3716915995397008</v>
       </c>
       <c r="M6">
-        <v>24.8018</v>
+        <v>3.8198</v>
       </c>
       <c r="N6">
-        <v>0.006759457102365639</v>
+        <v>0.02147161326587971</v>
       </c>
       <c r="O6">
-        <v>0.1353810043668122</v>
+        <v>0.1182600619195047</v>
       </c>
       <c r="P6">
-        <v>24.8018</v>
+        <v>3.8198</v>
       </c>
       <c r="Q6">
-        <v>0.006759457102365639</v>
+        <v>0.02147161326587971</v>
       </c>
       <c r="R6">
-        <v>0.1353810043668122</v>
+        <v>0.1182600619195047</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>585.6</v>
+        <v>223.7</v>
       </c>
       <c r="V6">
-        <v>0.1595988226316363</v>
+        <v>1.257448004496908</v>
       </c>
       <c r="W6">
-        <v>0.1373004571685528</v>
+        <v>0.1814606741573034</v>
       </c>
       <c r="X6">
-        <v>0.06605046952689242</v>
+        <v>0.0541345875174358</v>
       </c>
       <c r="Y6">
-        <v>0.07124998764166038</v>
+        <v>0.1273260866398676</v>
       </c>
       <c r="Z6">
-        <v>0.2018492672714585</v>
+        <v>5.364197530864192</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05847535159429378</v>
+        <v>0.05126086038812895</v>
       </c>
       <c r="AC6">
-        <v>-0.05847535159429378</v>
+        <v>-0.05126086038812895</v>
       </c>
       <c r="AD6">
-        <v>1287.9</v>
+        <v>31.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1287.9</v>
+        <v>31.7</v>
       </c>
       <c r="AG6">
-        <v>702.3000000000001</v>
+        <v>-192</v>
       </c>
       <c r="AH6">
-        <v>0.2598091626152387</v>
+        <v>0.1512404580152672</v>
       </c>
       <c r="AI6">
-        <v>0.5203636363636364</v>
+        <v>0.1258435887256848</v>
       </c>
       <c r="AJ6">
-        <v>0.160654237675855</v>
+        <v>13.61702127659575</v>
       </c>
       <c r="AK6">
-        <v>0.3717053032708796</v>
+        <v>-6.808510638297875</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nordfyns Bank A/S (CPSE:NRDF)</t>
+          <t>Danske Andelskassers Bank A/S (CPSE:DAB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,10 +1198,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.025</v>
+        <v>0.0587</v>
       </c>
       <c r="E7">
-        <v>-0.06809999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,82 +1216,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4.25</v>
+        <v>39.5</v>
       </c>
       <c r="L7">
-        <v>0.1534296028880867</v>
+        <v>0.3590909090909091</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.02348857390801273</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.2055696202531645</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.02348857390801273</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2055696202531645</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>105.9</v>
+        <v>146.2</v>
       </c>
       <c r="V7">
-        <v>2.088757396449704</v>
+        <v>0.4229100376048597</v>
       </c>
       <c r="W7">
-        <v>0.04685777287761852</v>
+        <v>0.1353203151764303</v>
       </c>
       <c r="X7">
-        <v>0.06450493194774953</v>
+        <v>0.05384903306435584</v>
       </c>
       <c r="Y7">
-        <v>-0.01764715907013101</v>
+        <v>0.08147128211207444</v>
       </c>
       <c r="Z7">
-        <v>3.597402597402596</v>
+        <v>0.5522088353413656</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05883560266067243</v>
+        <v>0.05139377109411364</v>
       </c>
       <c r="AC7">
-        <v>-0.05883560266067243</v>
+        <v>-0.05139377109411364</v>
       </c>
       <c r="AD7">
-        <v>13.1</v>
+        <v>52.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>13.1</v>
+        <v>52.2</v>
       </c>
       <c r="AG7">
-        <v>-92.80000000000001</v>
+        <v>-93.99999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.2053291536050157</v>
+        <v>0.1311887408896708</v>
       </c>
       <c r="AI7">
-        <v>0.1396588486140725</v>
+        <v>0.1180995475113122</v>
       </c>
       <c r="AJ7">
-        <v>2.204275534441805</v>
+        <v>-0.3734604688120778</v>
       </c>
       <c r="AK7">
-        <v>7.669421487603302</v>
+        <v>-0.3177822853279242</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1314,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Danske Andelskassers Bank A/S (CPSE:DAB)</t>
+          <t>Fynske Bank A/S (CPSE:FYNBK)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1323,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0076</v>
+        <v>0.0679</v>
       </c>
       <c r="E8">
-        <v>-0.00505</v>
+        <v>0.0842</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1341,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>15.8</v>
+        <v>20.6</v>
       </c>
       <c r="L8">
-        <v>0.1899038461538461</v>
+        <v>0.3280254777070064</v>
       </c>
       <c r="M8">
-        <v>9.880000000000001</v>
+        <v>1.43262</v>
       </c>
       <c r="N8">
-        <v>0.03594034194252456</v>
+        <v>0.008382796957284961</v>
       </c>
       <c r="O8">
-        <v>0.6253164556962025</v>
+        <v>0.06954466019417475</v>
       </c>
       <c r="P8">
-        <v>9.880000000000001</v>
+        <v>1.43262</v>
       </c>
       <c r="Q8">
-        <v>0.03594034194252456</v>
+        <v>0.008382796957284961</v>
       </c>
       <c r="R8">
-        <v>0.6253164556962025</v>
+        <v>0.06954466019417475</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1371,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>166.6</v>
+        <v>52.3</v>
       </c>
       <c r="V8">
-        <v>0.6060385594761731</v>
+        <v>0.3060269163253364</v>
       </c>
       <c r="W8">
-        <v>0.04574406485234511</v>
+        <v>0.1318822023047375</v>
       </c>
       <c r="X8">
-        <v>0.06429676329148318</v>
+        <v>0.05371965168148429</v>
       </c>
       <c r="Y8">
-        <v>-0.01855269843913807</v>
+        <v>0.07816255062325325</v>
       </c>
       <c r="Z8">
-        <v>0.88135593220339</v>
+        <v>0.8882602545968885</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.05888821789439044</v>
+        <v>0.05145608103990579</v>
       </c>
       <c r="AC8">
-        <v>-0.05888821789439044</v>
+        <v>-0.05145608103990579</v>
       </c>
       <c r="AD8">
-        <v>67.59999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>67.59999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="AG8">
-        <v>-99</v>
+        <v>-28.6</v>
       </c>
       <c r="AH8">
-        <v>0.1973722627737226</v>
+        <v>0.1217882836587873</v>
       </c>
       <c r="AI8">
-        <v>0.1804109954630371</v>
+        <v>0.1121628017037388</v>
       </c>
       <c r="AJ8">
-        <v>-0.5628197839681638</v>
+        <v>-0.2009838369641602</v>
       </c>
       <c r="AK8">
-        <v>-0.4757328207592503</v>
+        <v>-0.179874213836478</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1436,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fynske Bank A/S (CPSE:FYNBK)</t>
+          <t>Kreditbanken A/S (CPSE:KRE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1445,10 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0257</v>
+        <v>0.0868</v>
       </c>
       <c r="E9">
-        <v>-0.271</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1463,28 +1460,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>2.17</v>
+        <v>15.8</v>
       </c>
       <c r="L9">
-        <v>0.06235632183908046</v>
+        <v>0.3744075829383886</v>
       </c>
       <c r="M9">
-        <v>2.82734</v>
+        <v>1.19112</v>
       </c>
       <c r="N9">
-        <v>0.01996709039548023</v>
+        <v>0.01066356311548791</v>
       </c>
       <c r="O9">
-        <v>1.302921658986175</v>
+        <v>0.07538734177215189</v>
       </c>
       <c r="P9">
-        <v>2.82734</v>
+        <v>1.19112</v>
       </c>
       <c r="Q9">
-        <v>0.01996709039548023</v>
+        <v>0.01066356311548791</v>
       </c>
       <c r="R9">
-        <v>1.302921658986175</v>
+        <v>0.07538734177215189</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1493,182 +1490,60 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>105.7</v>
+        <v>144.7</v>
       </c>
       <c r="V9">
-        <v>0.7464689265536724</v>
+        <v>1.295434198746643</v>
       </c>
       <c r="W9">
-        <v>0.01172339276066991</v>
+        <v>0.1486359360301035</v>
       </c>
       <c r="X9">
-        <v>0.06257381260553026</v>
+        <v>0.05280862534472718</v>
       </c>
       <c r="Y9">
-        <v>-0.05085041984486035</v>
+        <v>0.09582731068537632</v>
       </c>
       <c r="Z9">
-        <v>0.455497382198953</v>
+        <v>16.6798418972332</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05936780386244181</v>
+        <v>0.05193615304685979</v>
       </c>
       <c r="AC9">
-        <v>-0.05936780386244181</v>
+        <v>-0.05193615304685979</v>
       </c>
       <c r="AD9">
-        <v>20.2</v>
+        <v>5.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>20.2</v>
+        <v>5.8</v>
       </c>
       <c r="AG9">
-        <v>-85.5</v>
+        <v>-138.9</v>
       </c>
       <c r="AH9">
-        <v>0.1248454882571075</v>
+        <v>0.04936170212765957</v>
       </c>
       <c r="AI9">
-        <v>0.1145124716553288</v>
+        <v>0.04305864884929472</v>
       </c>
       <c r="AJ9">
-        <v>-1.524064171122995</v>
+        <v>5.106617647058828</v>
       </c>
       <c r="AK9">
-        <v>-1.209335219236209</v>
+        <v>13.89000000000004</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Denmark</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kreditbanken A/S (CPSE:KRE)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.0299</v>
-      </c>
-      <c r="E10">
-        <v>-0.0115</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>6.35</v>
-      </c>
-      <c r="L10">
-        <v>0.2679324894514768</v>
-      </c>
-      <c r="M10">
-        <v>1.10712</v>
-      </c>
-      <c r="N10">
-        <v>0.01122839756592292</v>
-      </c>
-      <c r="O10">
-        <v>0.1743496062992126</v>
-      </c>
-      <c r="P10">
-        <v>1.10712</v>
-      </c>
-      <c r="Q10">
-        <v>0.01122839756592292</v>
-      </c>
-      <c r="R10">
-        <v>0.1743496062992126</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>107.6</v>
-      </c>
-      <c r="V10">
-        <v>1.091277890466531</v>
-      </c>
-      <c r="W10">
-        <v>0.05313807531380753</v>
-      </c>
-      <c r="X10">
-        <v>0.06084152867983689</v>
-      </c>
-      <c r="Y10">
-        <v>-0.007703453366029359</v>
-      </c>
-      <c r="Z10">
-        <v>1.169215589541194</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.05994609731359873</v>
-      </c>
-      <c r="AC10">
-        <v>-0.05994609731359873</v>
-      </c>
-      <c r="AD10">
-        <v>3.83</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>3.83</v>
-      </c>
-      <c r="AG10">
-        <v>-103.77</v>
-      </c>
-      <c r="AH10">
-        <v>0.03739138924143318</v>
-      </c>
-      <c r="AI10">
-        <v>0.03477708163079997</v>
-      </c>
-      <c r="AJ10">
-        <v>20.07156673114119</v>
-      </c>
-      <c r="AK10">
-        <v>-41.01581027667982</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
         <v>0</v>
       </c>
     </row>
